--- a/data/trans_dic/P04D$aparatos-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P04D$aparatos-Estudios-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, al menos, tiene aparatos de calefacción en su vivienda</t>
+          <t>Población que, al menos, tiene aparatos de calefacción en su vivienda (tasa de respuesta: 99,87%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>70,61; 76,46</t>
+          <t>70,68; 76,47</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>57,62; 64,75</t>
+          <t>57,08; 64,24</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>66,61; 73,99</t>
+          <t>66,75; 74,24</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>69,97; 74,94</t>
+          <t>70,03; 74,8</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>53,7; 60,5</t>
+          <t>54,07; 60,59</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>72,71; 77,66</t>
+          <t>72,88; 77,85</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>71,05; 74,94</t>
+          <t>71,07; 74,95</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>56,53; 61,47</t>
+          <t>56,42; 61,08</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>71,52; 75,58</t>
+          <t>71,28; 75,61</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>59,35; 63,96</t>
+          <t>59,19; 63,92</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>49,37; 53,74</t>
+          <t>49,42; 53,97</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>40,48; 66,88</t>
+          <t>40,25; 66,74</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>59,92; 64,84</t>
+          <t>60,07; 64,69</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>49,82; 54,39</t>
+          <t>49,78; 54,17</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>62,27; 76,04</t>
+          <t>62,4; 76,52</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>60,34; 63,51</t>
+          <t>60,35; 63,56</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>50,25; 53,24</t>
+          <t>50,4; 53,5</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>53,77; 69,15</t>
+          <t>52,38; 68,99</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>43,47; 53,28</t>
+          <t>44,05; 53,84</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>41,79; 50,95</t>
+          <t>42,16; 51,04</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>48,31; 56,97</t>
+          <t>49,37; 57,69</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>48,24; 58,56</t>
+          <t>48,29; 58,52</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>40,83; 49,54</t>
+          <t>40,84; 49,08</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>45,52; 52,75</t>
+          <t>46,26; 53,05</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>47,2; 54,17</t>
+          <t>47,53; 54,36</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>42,92; 48,85</t>
+          <t>42,78; 49,12</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>48,64; 53,9</t>
+          <t>48,67; 53,97</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>61,55; 64,91</t>
+          <t>61,59; 64,93</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>51,02; 54,65</t>
+          <t>51,3; 54,7</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>43,8; 64,76</t>
+          <t>46,54; 64,82</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>63,24; 66,62</t>
+          <t>63,38; 66,76</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>50,55; 53,97</t>
+          <t>50,65; 54,0</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>63,13; 72,28</t>
+          <t>62,87; 72,46</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>62,83; 65,22</t>
+          <t>62,96; 65,35</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>51,27; 53,8</t>
+          <t>51,44; 53,77</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>55,1; 66,48</t>
+          <t>55,92; 66,74</t>
         </is>
       </c>
     </row>
@@ -1099,7 +1099,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, al menos, tiene aparatos de calefacción en su vivienda</t>
+          <t>Población que, al menos, tiene aparatos de calefacción en su vivienda (tasa de respuesta: 99,87%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1306,47 +1306,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>686792; 743754</t>
+          <t>687493; 743852</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>434647; 488439</t>
+          <t>430610; 484584</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>341667; 379545</t>
+          <t>342398; 380825</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>935990; 1002538</t>
+          <t>936918; 1000628</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>534124; 601799</t>
+          <t>537821; 602659</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>548905; 586267</t>
+          <t>550182; 587672</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1641583; 1731488</t>
+          <t>1642012; 1731713</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>988801; 1075032</t>
+          <t>986725; 1068372</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>906742; 958219</t>
+          <t>903758; 958601</t>
         </is>
       </c>
     </row>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>2875660</t>
+          <t>2875661</t>
         </is>
       </c>
     </row>
@@ -1469,47 +1469,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1162627; 1252836</t>
+          <t>1159409; 1251990</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1025074; 1115790</t>
+          <t>1026113; 1120548</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>925585; 1529108</t>
+          <t>920143; 1525930</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1050780; 1137008</t>
+          <t>1053440; 1134474</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>990658; 1081348</t>
+          <t>989696; 1077022</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1390340; 1697777</t>
+          <t>1393306; 1708363</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2239888; 2357681</t>
+          <t>2240524; 2359704</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2042378; 2164216</t>
+          <t>2048596; 2174519</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2429843; 3124718</t>
+          <t>2367200; 3117734</t>
         </is>
       </c>
     </row>
@@ -1632,47 +1632,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>209186; 256384</t>
+          <t>211979; 259054</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>228553; 278646</t>
+          <t>230561; 279126</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>312395; 368398</t>
+          <t>319234; 373034</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>221264; 268555</t>
+          <t>221471; 268407</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>224205; 272039</t>
+          <t>224279; 269498</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>299641; 347254</t>
+          <t>304505; 349242</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>443611; 509132</t>
+          <t>446695; 510923</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>470458; 535387</t>
+          <t>468928; 538334</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>634675; 703346</t>
+          <t>635128; 704250</t>
         </is>
       </c>
     </row>
@@ -1795,47 +1795,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2100456; 2215281</t>
+          <t>2101717; 2215920</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1723097; 1845872</t>
+          <t>1732715; 1847514</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1509406; 2231546</t>
+          <t>1603874; 2233603</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2245067; 2364997</t>
+          <t>2249892; 2369972</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1785590; 1906330</t>
+          <t>1788931; 1907440</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2301579; 2635380</t>
+          <t>2292197; 2641725</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>4374508; 4541021</t>
+          <t>4383390; 4550326</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>3542702; 3717110</t>
+          <t>3554439; 3715132</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3907865; 4714883</t>
+          <t>3965990; 4732995</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P04D$aparatos-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P04D$aparatos-Estudios-trans_dic.xlsx
@@ -635,7 +635,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>70,71%</t>
+          <t>70,37%</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -650,7 +650,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>75,34%</t>
+          <t>74,94%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -665,7 +665,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>73,47%</t>
+          <t>73,06%</t>
         </is>
       </c>
     </row>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>70,68; 76,47</t>
+          <t>70,76; 76,48</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>57,08; 64,24</t>
+          <t>57,36; 64,7</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>66,75; 74,24</t>
+          <t>66,59; 74,04</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>70,03; 74,8</t>
+          <t>69,79; 74,69</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>54,07; 60,59</t>
+          <t>53,59; 59,89</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>72,88; 77,85</t>
+          <t>72,57; 77,22</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>71,07; 74,95</t>
+          <t>70,88; 74,74</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>56,42; 61,08</t>
+          <t>56,26; 61,18</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>71,28; 75,61</t>
+          <t>70,83; 74,98</t>
         </is>
       </c>
     </row>
@@ -745,7 +745,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>58,96%</t>
+          <t>65,9%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>68,42%</t>
+          <t>66,71%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -775,7 +775,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>63,63%</t>
+          <t>66,3%</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>59,19; 63,92</t>
+          <t>59,13; 63,53</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>49,42; 53,97</t>
+          <t>49,44; 53,89</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>40,25; 66,74</t>
+          <t>63,43; 68,32</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>60,07; 64,69</t>
+          <t>60,02; 64,6</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>49,78; 54,17</t>
+          <t>49,71; 54,24</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>62,4; 76,52</t>
+          <t>64,88; 68,66</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>60,35; 63,56</t>
+          <t>60,31; 63,45</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>50,4; 53,5</t>
+          <t>50,3; 53,41</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>52,38; 68,99</t>
+          <t>64,78; 67,8</t>
         </is>
       </c>
     </row>
@@ -855,7 +855,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>53,18%</t>
+          <t>52,87%</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>49,41%</t>
+          <t>48,8%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>51,28%</t>
+          <t>50,81%</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>44,05; 53,84</t>
+          <t>44,04; 53,38</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>42,16; 51,04</t>
+          <t>42,25; 51,5</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>49,37; 57,69</t>
+          <t>49,01; 57,14</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>48,29; 58,52</t>
+          <t>48,23; 58,05</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>40,84; 49,08</t>
+          <t>40,54; 49,22</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>46,26; 53,05</t>
+          <t>45,14; 51,78</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>47,53; 54,36</t>
+          <t>47,24; 54,17</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>42,78; 49,12</t>
+          <t>42,55; 48,9</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>48,67; 53,97</t>
+          <t>48,16; 53,36</t>
         </is>
       </c>
     </row>
@@ -965,7 +965,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>59,63%</t>
+          <t>63,99%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -980,7 +980,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>66,42%</t>
+          <t>65,0%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>63,12%</t>
+          <t>64,51%</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>61,59; 64,93</t>
+          <t>61,43; 64,97</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>51,3; 54,7</t>
+          <t>51,18; 54,74</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>46,54; 64,82</t>
+          <t>62,23; 65,91</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>63,38; 66,76</t>
+          <t>63,34; 66,67</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>50,65; 54,0</t>
+          <t>50,67; 53,91</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>62,87; 72,46</t>
+          <t>63,53; 66,41</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>62,96; 65,35</t>
+          <t>62,95; 65,33</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>51,44; 53,77</t>
+          <t>51,32; 53,89</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>55,92; 66,74</t>
+          <t>63,31; 65,64</t>
         </is>
       </c>
     </row>
@@ -1263,7 +1263,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>362680</t>
+          <t>405702</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>568757</t>
+          <t>615521</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>931437</t>
+          <t>1021224</t>
         </is>
       </c>
     </row>
@@ -1306,47 +1306,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>687493; 743852</t>
+          <t>688244; 743903</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>430610; 484584</t>
+          <t>432699; 488083</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>342398; 380825</t>
+          <t>383893; 426853</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>936918; 1000628</t>
+          <t>933584; 999241</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>537821; 602659</t>
+          <t>533060; 595673</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>550182; 587672</t>
+          <t>596077; 634248</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1642012; 1731713</t>
+          <t>1637760; 1726840</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>986725; 1068372</t>
+          <t>983993; 1069965</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>903758; 958601</t>
+          <t>990076; 1048134</t>
         </is>
       </c>
     </row>
@@ -1426,7 +1426,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1348107</t>
+          <t>1464980</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1527553</t>
+          <t>1444878</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>2875661</t>
+          <t>2909859</t>
         </is>
       </c>
     </row>
@@ -1469,47 +1469,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1159409; 1251990</t>
+          <t>1158298; 1244517</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1026113; 1120548</t>
+          <t>1026507; 1119016</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>920143; 1525930</t>
+          <t>1410114; 1518703</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1053440; 1134474</t>
+          <t>1052475; 1132851</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>989696; 1077022</t>
+          <t>988409; 1078495</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1393306; 1708363</t>
+          <t>1405211; 1487048</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2240524; 2359704</t>
+          <t>2238963; 2355361</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2048596; 2174519</t>
+          <t>2044527; 2171050</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2367200; 3117734</t>
+          <t>2843129; 2975648</t>
         </is>
       </c>
     </row>
@@ -1589,7 +1589,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>343848</t>
+          <t>376206</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1604,7 +1604,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>325267</t>
+          <t>357101</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>669115</t>
+          <t>733307</t>
         </is>
       </c>
     </row>
@@ -1632,47 +1632,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>211979; 259054</t>
+          <t>211909; 256876</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>230561; 279126</t>
+          <t>231075; 281621</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>319234; 373034</t>
+          <t>348773; 406619</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>221471; 268407</t>
+          <t>221198; 266249</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>224279; 269498</t>
+          <t>222633; 270312</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>304505; 349242</t>
+          <t>330320; 378926</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>446695; 510923</t>
+          <t>443933; 509056</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>468928; 538334</t>
+          <t>466411; 535976</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>635128; 704250</t>
+          <t>695091; 770204</t>
         </is>
       </c>
     </row>
@@ -1752,7 +1752,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2054635</t>
+          <t>2246889</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1767,7 +1767,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2421577</t>
+          <t>2417501</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>4476212</t>
+          <t>4664390</t>
         </is>
       </c>
     </row>
@@ -1795,47 +1795,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2101717; 2215920</t>
+          <t>2096305; 2217233</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1732715; 1847514</t>
+          <t>1728666; 1848960</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1603874; 2233603</t>
+          <t>2185001; 2314271</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2249892; 2369972</t>
+          <t>2248539; 2366648</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1788931; 1907440</t>
+          <t>1789862; 1904315</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2292197; 2641725</t>
+          <t>2362827; 2469674</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>4383390; 4550326</t>
+          <t>4383114; 4548999</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>3554439; 3715132</t>
+          <t>3545828; 3723876</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3965990; 4732995</t>
+          <t>4577129; 4745788</t>
         </is>
       </c>
     </row>
